--- a/Config/Excel/gm.xlsx
+++ b/Config/Excel/gm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,13 +67,13 @@
     <t>常用</t>
   </si>
   <si>
-    <t>测试战斗:1001;升一级:1002;</t>
+    <t>1001:测试战斗:参数;1002:升一级</t>
   </si>
   <si>
     <t>日志</t>
   </si>
   <si>
-    <t>查看日志:2001;</t>
+    <t>2001:查看日志;</t>
   </si>
   <si>
     <t>其他</t>

--- a/Config/Excel/gm.xlsx
+++ b/Config/Excel/gm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3D2648-85E1-460F-AE43-AC6CBB8E1F4F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4745405B-581D-45C3-B72C-5F32655B6B13}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="29865" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -101,6 +101,26 @@
   </si>
   <si>
     <t>战斗测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GM_Battle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GM_Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -571,6 +591,12 @@
       <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
@@ -585,6 +611,12 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="F6" t="s">
         <v>10</v>
       </c>
@@ -598,6 +630,12 @@
       </c>
       <c r="C7" s="3" t="s">
         <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
